--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486811_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486811_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6091</v>
+        <v>4.7636</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8543</v>
+        <v>4.9095</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2452</v>
+        <v>-0.1459</v>
       </c>
       <c r="G2" t="n">
         <v>3.1845</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1546</v>
+        <v>-0.0001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2211</v>
+        <v>-0.1659</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0665</v>
+        <v>0.1658</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8405</v>
+        <v>3.733</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0468</v>
+        <v>1.8399</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7938</v>
+        <v>1.8931</v>
       </c>
       <c r="G3" t="n">
         <v>2.2877</v>
@@ -688,13 +688,13 @@
         <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8384</v>
+        <v>0.7309</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7168</v>
+        <v>0.5099</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1216</v>
+        <v>0.221</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.373</v>
+        <v>3.5813</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6197</v>
+        <v>1.7783</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7533</v>
+        <v>1.803</v>
       </c>
       <c r="G4" t="n">
         <v>1.3816</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2537</v>
+        <v>0.462</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1107</v>
+        <v>0.0479</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3644</v>
+        <v>0.4141</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. JOAO</t>
+          <t>L. BLANCO CENTENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0451</v>
+        <v>1.7808</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9023</v>
+        <v>1.409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1429</v>
+        <v>0.3718</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2397</v>
+        <v>0.4844</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2344</v>
+        <v>0.4551</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9947</v>
+        <v>0.0294</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0405</v>
+        <v>1.0783</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9591</v>
+        <v>0.3865</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>0.6918</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8008</v>
+        <v>-0.5939</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2753</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0761</v>
+        <v>-0.6624</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3847</v>
+        <v>0.5241</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.3307</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5575</v>
+        <v>0.1933</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BLANCO CENTENO</t>
+          <t>A. JOAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5821</v>
+        <v>1.1777</v>
       </c>
       <c r="E6" t="n">
-        <v>1.409</v>
+        <v>1.2335</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1731</v>
+        <v>-0.0558</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4844</v>
+        <v>1.2397</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4551</v>
+        <v>2.2344</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0294</v>
+        <v>-0.9947</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0783</v>
+        <v>2.0405</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3865</v>
+        <v>1.9591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6918</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5939</v>
+        <v>-0.8008</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.2753</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6624</v>
+        <v>-1.0761</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3254</v>
+        <v>0.5172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3307</v>
+        <v>0.1584</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0053</v>
+        <v>0.3589</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. TSHIMANGA ZOLA</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2224</v>
+        <v>-0.1132</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6822</v>
+        <v>-0.855</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4598</v>
+        <v>0.7417</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5455</v>
+        <v>-0.3586</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.324</v>
+        <v>-0.0896</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2216</v>
+        <v>-0.269</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.283</v>
+        <v>-0.9858</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3237</v>
+        <v>-0.2963</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>-0.6895</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2626</v>
+        <v>0.6272</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0003</v>
+        <v>0.2068</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2623</v>
+        <v>0.4205</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1931</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2466</v>
+        <v>0.3379</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1582</v>
+        <v>0.1308</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.2071</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>K. TSHIMANGA ZOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5558</v>
+        <v>-0.1416</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3721</v>
+        <v>0.2685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8162</v>
+        <v>-0.4101</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3586</v>
+        <v>-0.5455</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0896</v>
+        <v>-0.324</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.269</v>
+        <v>-0.2216</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9858</v>
+        <v>-0.283</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2963</v>
+        <v>-0.3237</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6895</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6272</v>
+        <v>-0.2626</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2068</v>
+        <v>-0.0003</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>-0.2623</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1047</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3863</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2815</v>
+        <v>0.1381</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2856</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6764</v>
+        <v>-3.9867</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8929</v>
+        <v>-3.2032</v>
       </c>
       <c r="F9" t="n">
         <v>-0.7835</v>
@@ -1156,10 +1156,10 @@
         <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5515</v>
+        <v>0.2412</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1373</v>
+        <v>-0.173</v>
       </c>
       <c r="U9" t="n">
         <v>0.4142</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2677</v>
+        <v>-4.0802</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5863</v>
+        <v>-4.3242</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3186</v>
+        <v>0.2441</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9038</v>
@@ -1234,13 +1234,13 @@
         <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2979</v>
+        <v>-0.1104</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8556</v>
+        <v>-0.5936</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5577</v>
+        <v>0.4832</v>
       </c>
       <c r="V10" t="n">
         <v>0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9519</v>
+        <v>-4.2184</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4236</v>
+        <v>-2.541</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5284</v>
+        <v>-1.6774</v>
       </c>
       <c r="G11" t="n">
         <v>-5.576</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5956</v>
+        <v>0.138</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1865</v>
+        <v>-0.3039</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5909</v>
+        <v>0.4419</v>
       </c>
       <c r="V11" t="n">
         <v>1.7989</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.220400000000001</v>
+        <v>2.496300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2394000000000021</v>
+        <v>0.5153000000000003</v>
       </c>
       <c r="F12" t="n">
         <v>1.981</v>
@@ -1360,7 +1360,7 @@
         <v>-3.1023</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03390000000000093</v>
+        <v>0.03389999999999915</v>
       </c>
       <c r="J12" t="n">
         <v>6.6313</v>
@@ -1369,7 +1369,7 @@
         <v>1.3859</v>
       </c>
       <c r="L12" t="n">
-        <v>5.245299999999999</v>
+        <v>5.245300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-9.6998</v>
@@ -1378,10 +1378,10 @@
         <v>-4.488300000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.2114</v>
+        <v>-5.211399999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0.000200000000000089</v>
+        <v>0.0001999999999996449</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.5847</v>
@@ -1390,13 +1390,13 @@
         <v>11.5848</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4475</v>
+        <v>3.7234</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4098999999999999</v>
+        <v>0.6858000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0374</v>
+        <v>3.0376</v>
       </c>
       <c r="V12" t="n">
         <v>1.8415</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.34</v>
+        <v>4.3579</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6819</v>
+        <v>3.7853</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6582</v>
+        <v>0.5726</v>
       </c>
       <c r="G13" t="n">
         <v>4.8473</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7003</v>
+        <v>-0.6825</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4693</v>
+        <v>-0.3659</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.231</v>
+        <v>-0.3166</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.495</v>
+        <v>1.7226</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1366</v>
+        <v>1.24</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3584</v>
+        <v>0.4826</v>
       </c>
       <c r="G14" t="n">
         <v>1.8536</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3586</v>
+        <v>-0.131</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3979</v>
+        <v>1.2186</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4998</v>
+        <v>0.6606</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1019</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.342</v>
+        <v>0.9566</v>
       </c>
       <c r="H15" t="n">
-        <v>1.028</v>
+        <v>-0.5241</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.37</v>
+        <v>1.4807</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4798</v>
+        <v>1.971</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2357</v>
+        <v>-0.5927</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2442</v>
+        <v>2.5636</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8219</v>
+        <v>-1.0143</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2077</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6142</v>
+        <v>-1.0829</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0368</v>
+        <v>0.0689</v>
       </c>
       <c r="T15" t="n">
-        <v>1.02</v>
+        <v>-0.345</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0169</v>
+        <v>0.4139</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>V. DEL GROSSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7634</v>
+        <v>0.8037</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4537</v>
+        <v>0.421</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3097</v>
+        <v>0.3827</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9566</v>
+        <v>-0.1243</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5241</v>
+        <v>0.1651</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4807</v>
+        <v>-0.2893</v>
       </c>
       <c r="J16" t="n">
-        <v>1.971</v>
+        <v>0.8212</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5927</v>
+        <v>0.1655</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5636</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0143</v>
+        <v>-0.9454</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0829</v>
+        <v>-0.945</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3863</v>
+        <v>0.0551</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5518</v>
+        <v>-0.4002</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1655</v>
+        <v>0.4553</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6423</v>
+        <v>0.5471</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6049</v>
+        <v>1.3622</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2472</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.368</v>
+        <v>-0.342</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5587</v>
+        <v>1.028</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8093</v>
+        <v>-1.37</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5872000000000001</v>
+        <v>1.4798</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2474</v>
+        <v>1.2357</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6602</v>
+        <v>0.2442</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7808</v>
+        <v>-1.8219</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6887</v>
+        <v>-0.2077</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4695</v>
+        <v>-1.6142</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9644</v>
+        <v>0.1861</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3305</v>
+        <v>-0.1177</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6339</v>
+        <v>0.3037</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1698</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. DEL GROSSO</t>
+          <t>R. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3237</v>
+        <v>0.0757</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2142</v>
+        <v>-0.1173</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1095</v>
+        <v>0.193</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1243</v>
+        <v>0.0689</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1651</v>
+        <v>-0.2069</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2893</v>
+        <v>0.2758</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8212</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1655</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6556999999999999</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9454</v>
+        <v>0.0689</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0005</v>
+        <v>-0.2069</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.945</v>
+        <v>0.2758</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4249</v>
+        <v>0.0069</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.607</v>
+        <v>-0.1173</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1821</v>
+        <v>0.1242</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. PEREZ RUIZ</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1022</v>
+        <v>0.0388</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2207</v>
+        <v>-0.5951</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1185</v>
+        <v>0.6339</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0689</v>
+        <v>0.2386</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2069</v>
+        <v>0.3788</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2758</v>
+        <v>-0.1402</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.1035</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.5674</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0689</v>
+        <v>0.7025</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2069</v>
+        <v>0.2753</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2758</v>
+        <v>0.4272</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1711</v>
+        <v>-0.779</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2207</v>
+        <v>-0.1312</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0497</v>
+        <v>-0.6479</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2963</v>
+        <v>-0.3605</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9054</v>
+        <v>0.3651</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6091</v>
+        <v>-0.7255</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2386</v>
+        <v>2.0228</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3788</v>
+        <v>1.6407</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1402</v>
+        <v>0.3821</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4639</v>
+        <v>2.8106</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1035</v>
+        <v>1.7795</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5674</v>
+        <v>1.031</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7025</v>
+        <v>-0.7877</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2753</v>
+        <v>-0.1388</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4272</v>
+        <v>-0.6489</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1141</v>
+        <v>-0.4412</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4415</v>
+        <v>-0.8003</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6727</v>
+        <v>0.3591</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.5559</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0114</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0486</v>
+        <v>-3.0186</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9628</v>
+        <v>2.4415</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0228</v>
+        <v>-1.368</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6407</v>
+        <v>-0.5587</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3821</v>
+        <v>-0.8093</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8106</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7795</v>
+        <v>-1.2474</v>
       </c>
       <c r="L21" t="n">
-        <v>1.031</v>
+        <v>0.6602</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7877</v>
+        <v>-0.7808</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1388</v>
+        <v>0.6887</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6489</v>
+        <v>-1.4695</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3862</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0921</v>
+        <v>0.745</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.214</v>
+        <v>-0.0832</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1219</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5559</v>
+        <v>2.1698</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8415</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.601</v>
+        <v>-1.27</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1178</v>
+        <v>-0.911</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4831</v>
+        <v>-0.359</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0012</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0205</v>
+        <v>-0.6895</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7446</v>
+        <v>-0.6204</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9094</v>
+        <v>-2.5176</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5448</v>
+        <v>-1.8551</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3645</v>
+        <v>-0.6625</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1522</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2428</v>
+        <v>-0.3654</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0273</v>
+        <v>-0.283</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2155</v>
+        <v>-0.0825</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2627</v>
+        <v>-5.5703</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.525</v>
+        <v>-3.3181</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7377</v>
+        <v>-2.2522</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9318</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4235</v>
+        <v>-0.7311</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4693</v>
+        <v>-0.2625</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.4686</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3282</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.220699999999999</v>
+        <v>-1.531099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.981</v>
+        <v>-1.981000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2393999999999998</v>
+        <v>0.4500999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>3.068300000000001</v>
+        <v>3.068299999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1024</v>
+        <v>3.102399999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-0.03399999999999981</v>
       </c>
       <c r="J25" t="n">
-        <v>9.6998</v>
+        <v>9.699800000000003</v>
       </c>
       <c r="K25" t="n">
         <v>4.488199999999999</v>
@@ -2392,10 +2392,10 @@
         <v>-1.386</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.2453</v>
+        <v>-5.245299999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>3.33066907387547e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-11.5848</v>
@@ -2404,13 +2404,13 @@
         <v>11.5847</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4474</v>
+        <v>-2.7577</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0372</v>
+        <v>-3.037500000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4099000000000003</v>
+        <v>0.2793999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8414</v>
